--- a/docs/testing/stress-test-scenarios.xlsx
+++ b/docs/testing/stress-test-scenarios.xlsx
@@ -497,7 +497,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -582,7 +582,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -722,7 +722,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -807,7 +807,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1195,9 +1195,9 @@
       <c r="I2" s="11" t="n"/>
       <c r="J2" s="11" t="n"/>
       <c r="K2" s="11" t="n"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1241,9 +1241,9 @@
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="11" t="n"/>
       <c r="K3" s="11" t="n"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1287,9 +1287,9 @@
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="11" t="n"/>
       <c r="K4" s="11" t="n"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -1333,9 +1333,9 @@
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n"/>
       <c r="K5" s="11" t="n"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1379,9 +1379,9 @@
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -1425,9 +1425,9 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1471,9 +1471,9 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -1517,9 +1517,9 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="11" t="n"/>
       <c r="K9" s="11" t="n"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1563,9 +1563,9 @@
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="11" t="n"/>
       <c r="K10" s="11" t="n"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1609,9 +1609,9 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
       <c r="K11" s="11" t="n"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>تا حدی — پیش‌پرداخت قاعده دارد</t>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="11" t="n"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -1701,7 +1701,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="11" t="n"/>
       <c r="K13" s="11" t="n"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -1747,7 +1747,7 @@
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="11" t="n"/>
       <c r="K14" s="11" t="n"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -1793,7 +1793,7 @@
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="11" t="n"/>
       <c r="K15" s="11" t="n"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -1839,7 +1839,7 @@
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="11" t="n"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -1885,9 +1885,9 @@
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="11" t="n"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -1977,7 +1977,7 @@
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="11" t="n"/>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2023,7 +2023,7 @@
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="11" t="n"/>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2069,7 +2069,7 @@
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="11" t="n"/>
       <c r="K21" s="11" t="n"/>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="11" t="n"/>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2201,9 +2201,9 @@
       </c>
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="11" t="n"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — چک: بابت معاملهٔ تازه یا حساب قبلی</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="11" t="n"/>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2289,9 +2289,9 @@
       </c>
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان ارزش افزوده</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="11" t="n"/>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="11" t="n"/>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="11" t="n"/>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2553,9 +2553,9 @@
       </c>
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="11" t="n"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L32" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان اول تسویه</t>
         </is>
       </c>
     </row>
@@ -2597,9 +2597,9 @@
       </c>
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L33" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان اول تسویه</t>
         </is>
       </c>
     </row>
@@ -2641,9 +2641,9 @@
       </c>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="11" t="n"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L34" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان اول تسویه</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2729,9 +2729,9 @@
       </c>
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L36" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان اول تسویه</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2817,9 +2817,9 @@
       </c>
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="11" t="n"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — امتناع وقتی ماهیت یا مبلغ روشن نیست</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -2949,9 +2949,9 @@
       </c>
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — امتناع وقتی ماهیت یا مبلغ روشن نیست</t>
         </is>
       </c>
     </row>
@@ -2993,9 +2993,9 @@
       </c>
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — چک: بابت معاملهٔ تازه یا حساب قبلی</t>
         </is>
       </c>
     </row>
@@ -3037,9 +3037,9 @@
       </c>
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L43" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — چک: بابت معاملهٔ تازه یا حساب قبلی</t>
         </is>
       </c>
     </row>
@@ -3081,9 +3081,9 @@
       </c>
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="11" t="n"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L44" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3125,9 +3125,9 @@
       </c>
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="n"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L45" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3169,9 +3169,9 @@
       </c>
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="11" t="n"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L46" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3213,9 +3213,9 @@
       </c>
       <c r="I47" s="11" t="n"/>
       <c r="J47" s="11" t="n"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L47" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3257,9 +3257,9 @@
       </c>
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="11" t="n"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L48" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3301,9 +3301,9 @@
       </c>
       <c r="I49" s="11" t="n"/>
       <c r="J49" s="11" t="n"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L49" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3345,9 +3345,9 @@
       </c>
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="11" t="n"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L50" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -3389,9 +3389,9 @@
       </c>
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="11" t="n"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>تا حدی — چک دریافتی سؤال می‌پرسد</t>
+      <c r="L51" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — چک: بابت معاملهٔ تازه یا حساب قبلی</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="I52" s="11" t="n"/>
       <c r="J52" s="11" t="n"/>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="11" t="n"/>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="11" t="n"/>
-      <c r="L54" t="inlineStr">
+      <c r="L54" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="11" t="n"/>
-      <c r="L55" t="inlineStr">
+      <c r="L55" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3609,9 +3609,9 @@
       </c>
       <c r="I56" s="11" t="n"/>
       <c r="J56" s="11" t="n"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L56" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — بدهی تحقق‌یافته پیش از پرداخت</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="11" t="n"/>
-      <c r="L57" t="inlineStr">
+      <c r="L57" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="11" t="n"/>
-      <c r="L58" t="inlineStr">
+      <c r="L58" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="11" t="n"/>
-      <c r="L59" t="inlineStr">
+      <c r="L59" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="11" t="n"/>
-      <c r="L60" t="inlineStr">
+      <c r="L60" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I61" s="11" t="n"/>
       <c r="J61" s="11" t="n"/>
-      <c r="L61" t="inlineStr">
+      <c r="L61" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="11" t="n"/>
-      <c r="L62" t="inlineStr">
+      <c r="L62" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -3917,9 +3917,9 @@
       </c>
       <c r="I63" s="11" t="n"/>
       <c r="J63" s="11" t="n"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L63" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — پیش‌پرداخت و دورهٔ پوشش</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="11" t="n"/>
-      <c r="L64" t="inlineStr">
+      <c r="L64" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="I65" s="11" t="n"/>
       <c r="J65" s="11" t="n"/>
-      <c r="L65" t="inlineStr">
+      <c r="L65" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="11" t="n"/>
-      <c r="L66" t="inlineStr">
+      <c r="L66" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
-      <c r="L67" t="inlineStr">
+      <c r="L67" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="11" t="n"/>
-      <c r="L68" t="inlineStr">
+      <c r="L68" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4181,9 +4181,9 @@
       </c>
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="11" t="n"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — بدهی تحقق‌یافته پیش از پرداخت</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="I70" s="11" t="n"/>
       <c r="J70" s="11" t="n"/>
-      <c r="L70" t="inlineStr">
+      <c r="L70" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I71" s="11" t="n"/>
       <c r="J71" s="11" t="n"/>
-      <c r="L71" t="inlineStr">
+      <c r="L71" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4313,9 +4313,9 @@
       </c>
       <c r="I72" s="11" t="n"/>
       <c r="J72" s="11" t="n"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان ارزش افزوده</t>
         </is>
       </c>
     </row>
@@ -4357,9 +4357,9 @@
       </c>
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="11" t="n"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -4401,9 +4401,9 @@
       </c>
       <c r="I74" s="11" t="n"/>
       <c r="J74" s="11" t="n"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان ارزش افزوده</t>
         </is>
       </c>
     </row>
@@ -4445,9 +4445,9 @@
       </c>
       <c r="I75" s="11" t="n"/>
       <c r="J75" s="11" t="n"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L75" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان ارزش افزوده</t>
         </is>
       </c>
     </row>
@@ -4489,9 +4489,9 @@
       </c>
       <c r="I76" s="11" t="n"/>
       <c r="J76" s="11" t="n"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L76" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -4533,9 +4533,9 @@
       </c>
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="11" t="n"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L77" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان ارزش افزوده</t>
         </is>
       </c>
     </row>
@@ -4577,9 +4577,9 @@
       </c>
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="11" t="n"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L78" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -4621,9 +4621,9 @@
       </c>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="11" t="n"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L79" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -4665,9 +4665,9 @@
       </c>
       <c r="I80" s="11" t="n"/>
       <c r="J80" s="11" t="n"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L80" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — نگهبان ارزش افزوده</t>
         </is>
       </c>
     </row>
@@ -4709,9 +4709,9 @@
       </c>
       <c r="I81" s="11" t="n"/>
       <c r="J81" s="11" t="n"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>تا حدی — تفکیک ارزش افزوده</t>
+      <c r="L81" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -4753,9 +4753,9 @@
       </c>
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="11" t="n"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L82" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — جابه‌جایی مالک به حسابدار</t>
         </is>
       </c>
     </row>
@@ -4797,9 +4797,9 @@
       </c>
       <c r="I83" s="11" t="n"/>
       <c r="J83" s="11" t="n"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L83" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — جابه‌جایی مالک به حسابدار</t>
         </is>
       </c>
     </row>
@@ -4841,9 +4841,9 @@
       </c>
       <c r="I84" s="11" t="n"/>
       <c r="J84" s="11" t="n"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L84" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — جابه‌جایی مالک به حسابدار</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="I85" s="11" t="n"/>
       <c r="J85" s="11" t="n"/>
-      <c r="L85" t="inlineStr">
+      <c r="L85" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="I86" s="11" t="n"/>
       <c r="J86" s="11" t="n"/>
-      <c r="L86" t="inlineStr">
+      <c r="L86" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="I87" s="11" t="n"/>
       <c r="J87" s="11" t="n"/>
-      <c r="L87" t="inlineStr">
+      <c r="L87" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="11" t="n"/>
-      <c r="L88" t="inlineStr">
+      <c r="L88" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="I89" s="11" t="n"/>
       <c r="J89" s="11" t="n"/>
-      <c r="L89" t="inlineStr">
+      <c r="L89" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I90" s="11" t="n"/>
       <c r="J90" s="11" t="n"/>
-      <c r="L90" t="inlineStr">
+      <c r="L90" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5149,9 +5149,9 @@
       </c>
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -5193,9 +5193,9 @@
       </c>
       <c r="I92" s="11" t="n"/>
       <c r="J92" s="11" t="n"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5237,9 +5237,9 @@
       </c>
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="11" t="n"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5281,9 +5281,9 @@
       </c>
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L94" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5325,9 +5325,9 @@
       </c>
       <c r="I95" s="11" t="n"/>
       <c r="J95" s="11" t="n"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L95" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5369,9 +5369,9 @@
       </c>
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="11" t="n"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L96" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5413,9 +5413,9 @@
       </c>
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="11" t="n"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L97" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5457,9 +5457,9 @@
       </c>
       <c r="I98" s="11" t="n"/>
       <c r="J98" s="11" t="n"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L98" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5501,9 +5501,9 @@
       </c>
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="11" t="n"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L99" s="0" t="inlineStr">
+        <is>
+          <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
       </c>
     </row>
@@ -5545,9 +5545,9 @@
       </c>
       <c r="I100" s="11" t="n"/>
       <c r="J100" s="11" t="n"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — چک: بابت معاملهٔ تازه یا حساب قبلی</t>
         </is>
       </c>
     </row>
@@ -5589,9 +5589,9 @@
       </c>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="11" t="n"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>تا حدی — نگهبان تسویه</t>
+      <c r="L101" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — امتناع وقتی ماهیت یا مبلغ روشن نیست</t>
         </is>
       </c>
     </row>
@@ -5633,9 +5633,9 @@
       </c>
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="11" t="n"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L102" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -5677,9 +5677,9 @@
       </c>
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="11" t="n"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L103" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -5721,9 +5721,9 @@
       </c>
       <c r="I104" s="11" t="n"/>
       <c r="J104" s="11" t="n"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L104" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="11" t="n"/>
-      <c r="L105" t="inlineStr">
+      <c r="L105" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="11" t="n"/>
-      <c r="L106" t="inlineStr">
+      <c r="L106" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5853,9 +5853,9 @@
       </c>
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="11" t="n"/>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L107" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="11" t="n"/>
-      <c r="L108" t="inlineStr">
+      <c r="L108" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -5941,9 +5941,9 @@
       </c>
       <c r="I109" s="11" t="n"/>
       <c r="J109" s="11" t="n"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L109" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -5985,9 +5985,9 @@
       </c>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="11" t="n"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — اصلاح اشتباه و تغییر برآورد</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="11" t="n"/>
-      <c r="L111" t="inlineStr">
+      <c r="L111" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="11" t="n"/>
-      <c r="L112" t="inlineStr">
+      <c r="L112" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="11" t="n"/>
-      <c r="L113" t="inlineStr">
+      <c r="L113" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="11" t="n"/>
-      <c r="L114" t="inlineStr">
+      <c r="L114" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="I115" s="11" t="n"/>
       <c r="J115" s="11" t="n"/>
-      <c r="L115" t="inlineStr">
+      <c r="L115" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="11" t="n"/>
-      <c r="L116" t="inlineStr">
+      <c r="L116" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I117" s="11" t="n"/>
       <c r="J117" s="11" t="n"/>
-      <c r="L117" t="inlineStr">
+      <c r="L117" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="I118" s="11" t="n"/>
       <c r="J118" s="11" t="n"/>
-      <c r="L118" t="inlineStr">
+      <c r="L118" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="I119" s="11" t="n"/>
       <c r="J119" s="11" t="n"/>
-      <c r="L119" t="inlineStr">
+      <c r="L119" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="11" t="n"/>
-      <c r="L120" t="inlineStr">
+      <c r="L120" s="0" t="inlineStr">
         <is>
           <t>خیر — قاعده‌اش ساخته نشده</t>
         </is>
@@ -6469,9 +6469,9 @@
       </c>
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="11" t="n"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>خیر — قاعده‌اش ساخته نشده</t>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t>تا حدی — امتناع وقتی ماهیت یا مبلغ روشن نیست</t>
         </is>
       </c>
     </row>
@@ -18668,7 +18668,7 @@
         <f>IF(D21=0, 0, AVERAGEIFS('نتایج تست و امتیازدهی'!$H$2:$H$121, 'نتایج تست و امتیازدهی'!$B$2:$B$121, B21, 'نتایج تست و امتیازدهی'!$H$2:$H$121, "&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="G21">
+      <c r="G21" s="0">
         <f>COUNTIF('تست کور'!$L$2:$L$121, "تا حدی*")</f>
         <v/>
       </c>
@@ -18701,7 +18701,7 @@
         <f>IFERROR(AVERAGE('نتایج تست و امتیازدهی'!$H$2:$H$121), 0)</f>
         <v/>
       </c>
-      <c r="G22">
+      <c r="G22" s="0">
         <f>COUNTIFS('تست کور'!$L$2:$L$121, "تا حدی*", 'تست کور'!$I$2:$I$121, "&lt;&gt;")</f>
         <v/>
       </c>
@@ -18982,6 +18982,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="52" t="inlineStr">
         <is>
@@ -19033,7 +19034,7 @@
       </c>
       <c r="C21" s="53" t="inlineStr">
         <is>
-          <t>در سطح سرفصل، نه تک‌تک سناریو. «تا حدی» یعنی بخشی از آن سرفصل قاعده دارد؛ پیش از آزمون هر سناریو خودت کنترل کن که واقعاً در دامنه است یا نه.</t>
+          <t>سناریو به سناریو، با اجرای هر ۱۲۰ جمله روی موتور واقعی (پایان فاز ۲). «تا حدی — …» یعنی قاعده یا نگهبانی برای همین سناریو ساخته شده و نام آن کنار برچسب آمده. رفتار مورد انتظار هر کدام در test/stress-scenarios.test.js قفل شده است: ثبت درست، سؤال مرتبط، یا صف حسابدار.</t>
         </is>
       </c>
     </row>
